--- a/chinni-treasure/chinni-treasure-export-2026-07-18.xlsx
+++ b/chinni-treasure/chinni-treasure-export-2026-07-18.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="301">
   <si>
     <t>ID</t>
   </si>
@@ -287,6 +287,46 @@
     <t>7/3/2026, 4:37:45 PM</t>
   </si>
   <si>
+    <t>c6fd6319-543b-4e0e-85ff-8594885a526a</t>
+  </si>
+  <si>
+    <t>0011</t>
+  </si>
+  <si>
+    <t>Sparkly Rose Gold Clutch</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Sparkly Rose Gold Clutch
+## 🛍️ Product Details
+- **Price:** 850Rs  
+- **Color:** Rose Gold
+## ✨ Features
+- Detachable gold chain, designer shimmer textured finish, a structured rectangular shape with rounded edges and a gold-tone top clasp.
+## ✨ Description
+- A beautiful clutch that combines sparkle elegance &amp; convenience in one luxurious design.
+- This elegant clutch is designed to elevate any outfit with its shimmering finish &amp; premium gold frame detailing.
+- Compact shape makes it easy to carry boldly &amp; glow beautifully.
+## 💎 Why Choose This Treasure?
+- Luxury clutch offered in a cost-effective range.
+- Crafted with meticulous attention.
+- Intricately embellished with premium designer finish details.
+- Exceptional craftsmanship to create a bold and eye-catching look.
+- Rare to find in other social platforms.
+- Premium rose gold finish and spacious to keep your things safe.</t>
+  </si>
+  <si>
+    <t>850</t>
+  </si>
+  <si>
+    <t>https://i.imgur.gg/nlrXFTJ-IMG_20260705_174428.jpg</t>
+  </si>
+  <si>
+    <t>7/18/2026, 7:31:08 AM</t>
+  </si>
+  <si>
+    <t>7/18/2026, 8:26:00 AM</t>
+  </si>
+  <si>
     <t>f66837d7-4c09-4d84-8efe-a5cde13396be</t>
   </si>
   <si>
@@ -397,6 +437,43 @@
   </si>
   <si>
     <t>7/2/2026, 5:47:51 AM</t>
+  </si>
+  <si>
+    <t>b6191e5f-945a-4cbd-87cb-c61dbf619f99</t>
+  </si>
+  <si>
+    <t>0010</t>
+  </si>
+  <si>
+    <t>Sparkly Gold Clutch</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Sparkly Gold Clutch
+## 🛍️ Product Details
+- **Price:** 850Rs  
+- **Color:** Gold
+## ✨ Features
+- Detachable gold chain, designer shimmer textured finish, a structured rectangular shape with rounded edges and a gold-tone top clasp.
+## ✨ Description
+- A beautiful clutch that combines sparkle elegance &amp; convenience in one luxurious design.
+- This elegant clutch is designed to elevate any outfit with its shimmering finish &amp; premium gold frame detailing.
+- Compact shape makes it easy to carry boldly &amp; glow beautifully.
+## 💎 Why Choose This Treasure?
+- Luxury clutch offered in a cost-effective range.
+- Crafted with meticulous attention.
+- Intricately embellished with premium designer finish.
+- Exceptional craftsmanship to create a bold and eye-catching look.
+- Rare to find in other social platforms.
+- Premium gold finish and spacious to keep your things safe.</t>
+  </si>
+  <si>
+    <t>https://i.imgur.gg/yqos8ez-IMG_20260705_175739.jpg</t>
+  </si>
+  <si>
+    <t>7/18/2026, 7:20:43 AM</t>
+  </si>
+  <si>
+    <t>7/18/2026, 8:23:10 AM</t>
   </si>
   <si>
     <t>1d8788a8-8fd1-4a48-a36a-51cd3784c97d</t>
@@ -1122,6 +1199,9 @@
     <t>0013 - Designer Bangle Organizer Box</t>
   </si>
   <si>
+    <t>0011 - Sparkly Rose Gold Clutch</t>
+  </si>
+  <si>
     <t>0008 - Silver Sparkle Clutch</t>
   </si>
   <si>
@@ -1129,6 +1209,9 @@
   </si>
   <si>
     <t>0016 - Multicolor Bangles(Set of 32 pcs)</t>
+  </si>
+  <si>
+    <t>0010 - Sparkly Gold Clutch</t>
   </si>
   <si>
     <t>0012 - Designer Bangle Organizer Box</t>
@@ -1740,7 +1823,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -1982,36 +2065,36 @@
         <v>68</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="K6" t="s">
         <v>10</v>
       </c>
       <c r="L6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D7">
         <v>4</v>
@@ -2020,10 +2103,10 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -2093,48 +2176,48 @@
         <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J9" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s">
         <v>10</v>
       </c>
       <c r="L9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -2143,80 +2226,80 @@
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H10">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J10" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="K10" t="s">
         <v>10</v>
       </c>
       <c r="L10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="M10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J11" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="K11" t="s">
         <v>10</v>
       </c>
       <c r="L11" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D12">
         <v>4</v>
@@ -2225,25 +2308,25 @@
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="K12" t="s">
         <v>10</v>
       </c>
       <c r="L12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s">
         <v>114</v>
@@ -2260,16 +2343,16 @@
         <v>117</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
         <v>118</v>
       </c>
       <c r="G13" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -2278,7 +2361,7 @@
         <v>119</v>
       </c>
       <c r="J13" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="K13" t="s">
         <v>10</v>
@@ -2310,13 +2393,13 @@
         <v>125</v>
       </c>
       <c r="G14" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J14" t="s">
         <v>53</v>
@@ -2325,21 +2408,21 @@
         <v>10</v>
       </c>
       <c r="L14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -2348,16 +2431,16 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J15" t="s">
         <v>53</v>
@@ -2366,21 +2449,21 @@
         <v>10</v>
       </c>
       <c r="L15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D16">
         <v>4</v>
@@ -2389,10 +2472,10 @@
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G16" t="s">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -2401,7 +2484,7 @@
         <v>141</v>
       </c>
       <c r="J16" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="K16" t="s">
         <v>10</v>
@@ -2423,34 +2506,46 @@
       <c r="C17" t="s">
         <v>146</v>
       </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
       <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
         <v>147</v>
       </c>
       <c r="G17" t="s">
+        <v>51</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
         <v>148</v>
       </c>
-      <c r="H17">
-        <v>0</v>
+      <c r="J17" t="s">
+        <v>53</v>
       </c>
       <c r="K17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" t="s">
         <v>149</v>
       </c>
-      <c r="L17" t="s">
+      <c r="M17" t="s">
         <v>150</v>
-      </c>
-      <c r="M17" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B18" t="s">
         <v>152</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>153</v>
-      </c>
-      <c r="C18" t="s">
-        <v>154</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -2459,10 +2554,10 @@
         <v>8</v>
       </c>
       <c r="F18" t="s">
+        <v>154</v>
+      </c>
+      <c r="G18" t="s">
         <v>155</v>
-      </c>
-      <c r="G18" t="s">
-        <v>51</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -2471,7 +2566,7 @@
         <v>156</v>
       </c>
       <c r="J18" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="K18" t="s">
         <v>10</v>
@@ -2493,46 +2588,34 @@
       <c r="C19" t="s">
         <v>161</v>
       </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
       <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
         <v>162</v>
       </c>
       <c r="G19" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" t="s">
-        <v>163</v>
-      </c>
-      <c r="J19" t="s">
-        <v>62</v>
-      </c>
       <c r="K19" t="s">
-        <v>10</v>
+        <v>164</v>
       </c>
       <c r="L19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -2541,19 +2624,19 @@
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G20" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="s">
         <v>171</v>
       </c>
       <c r="J20" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K20" t="s">
         <v>10</v>
@@ -2563,6 +2646,88 @@
       </c>
       <c r="M20" t="s">
         <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>174</v>
+      </c>
+      <c r="B21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C21" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>177</v>
+      </c>
+      <c r="G21" t="s">
+        <v>155</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21" t="s">
+        <v>178</v>
+      </c>
+      <c r="J21" t="s">
+        <v>62</v>
+      </c>
+      <c r="K21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" t="s">
+        <v>179</v>
+      </c>
+      <c r="M21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>181</v>
+      </c>
+      <c r="B22" t="s">
+        <v>182</v>
+      </c>
+      <c r="C22" t="s">
+        <v>183</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>184</v>
+      </c>
+      <c r="G22" t="s">
+        <v>185</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22" t="s">
+        <v>186</v>
+      </c>
+      <c r="J22" t="s">
+        <v>36</v>
+      </c>
+      <c r="K22" t="s">
+        <v>10</v>
+      </c>
+      <c r="L22" t="s">
+        <v>187</v>
+      </c>
+      <c r="M22" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -2599,58 +2764,58 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>6</v>
@@ -2661,117 +2826,117 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C2" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="D2" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="E2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="F2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="G2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="H2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="I2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="J2" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="K2" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="L2" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="M2" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="N2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="O2" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="P2" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="Q2" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="T2" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="U2" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="C3" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="D3" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="E3" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="F3" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="G3" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="H3" t="s">
+        <v>232</v>
+      </c>
+      <c r="I3" t="s">
+        <v>233</v>
+      </c>
+      <c r="J3" t="s">
+        <v>234</v>
+      </c>
+      <c r="K3" t="s">
         <v>217</v>
       </c>
-      <c r="I3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J3" t="s">
-        <v>219</v>
-      </c>
-      <c r="K3" t="s">
-        <v>202</v>
-      </c>
       <c r="L3" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="N3" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="O3" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="P3" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="Q3" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="T3" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="U3" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -2798,19 +2963,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -2818,48 +2983,48 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="E2" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="B3" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C3" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="E3" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="F3">
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -2885,13 +3050,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>6</v>
@@ -2899,104 +3064,104 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="C2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D2" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="E2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="C3" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D3" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C4" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="D4" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="E4" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C5" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="D5" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="E5" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="B6" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C6" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="D6" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="E6" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="B7" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="C7" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D7" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="E7" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -3024,19 +3189,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -3047,28 +3212,28 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="B2" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="C2" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="D2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="G2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="H2" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3080,7 +3245,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -3090,18 +3255,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3112,7 +3277,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -3123,7 +3288,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -3134,7 +3299,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -3145,7 +3310,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B6">
         <v>25</v>
@@ -3156,244 +3321,266 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B8" t="s">
         <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B9" t="s">
         <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B10" t="s">
         <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B11" t="s">
         <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B13" t="s">
         <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B14" t="s">
         <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C16" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B18" t="s">
         <v>115</v>
       </c>
       <c r="C18" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B19" t="s">
         <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C20" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C21" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B22" t="s">
         <v>144</v>
       </c>
       <c r="C22" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B23" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C23" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B24" t="s">
         <v>159</v>
       </c>
       <c r="C24" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C25" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s">
-        <v>252</v>
+        <v>174</v>
       </c>
       <c r="C26" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="B27" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C27" t="s">
-        <v>193</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="B28" t="s">
-        <v>210</v>
+        <v>267</v>
       </c>
       <c r="C28" t="s">
-        <v>211</v>
+        <v>299</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>300</v>
+      </c>
+      <c r="B29" t="s">
+        <v>207</v>
+      </c>
+      <c r="C29" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>300</v>
+      </c>
+      <c r="B30" t="s">
+        <v>225</v>
+      </c>
+      <c r="C30" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/chinni-treasure/chinni-treasure-export-2026-07-18.xlsx
+++ b/chinni-treasure/chinni-treasure-export-2026-07-18.xlsx
@@ -1,23 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01D7E2FF-0AAF-4A74-8AD6-164946B883F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="16200" windowHeight="9307" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Categories" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Products" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Orders" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Order Items" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Order Status History" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="Admins" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="ID Lookup" state="visible" r:id="rId10"/>
+    <sheet name="Categories" sheetId="1" r:id="rId1"/>
+    <sheet name="Products" sheetId="2" r:id="rId2"/>
+    <sheet name="Orders" sheetId="3" r:id="rId3"/>
+    <sheet name="Order Items" sheetId="4" r:id="rId4"/>
+    <sheet name="Order Status History" sheetId="5" r:id="rId5"/>
+    <sheet name="Admins" sheetId="6" r:id="rId6"/>
+    <sheet name="ID Lookup" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="487" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="278">
   <si>
     <t>ID</t>
   </si>
@@ -52,28 +56,34 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>5/24/2026, 6:01:52 AM</t>
-  </si>
-  <si>
-    <t>6/27/2026, 5:47:57 AM</t>
-  </si>
-  <si>
-    <t>Apparel</t>
-  </si>
-  <si>
-    <t>apparel</t>
-  </si>
-  <si>
-    <t>Watches</t>
-  </si>
-  <si>
-    <t>watches</t>
-  </si>
-  <si>
-    <t>Home</t>
-  </si>
-  <si>
-    <t>home</t>
+    <t>18/7/2026, 2:05:14 pm</t>
+  </si>
+  <si>
+    <t>18/7/2026, 4:27:52 pm</t>
+  </si>
+  <si>
+    <t>Bangles</t>
+  </si>
+  <si>
+    <t>bangles</t>
+  </si>
+  <si>
+    <t>18/7/2026, 4:05:59 pm</t>
+  </si>
+  <si>
+    <t>18/7/2026, 4:11:47 pm</t>
+  </si>
+  <si>
+    <t>Bracelets</t>
+  </si>
+  <si>
+    <t>bracelet</t>
+  </si>
+  <si>
+    <t>18/7/2026, 4:07:08 pm</t>
+  </si>
+  <si>
+    <t>18/7/2026, 4:11:52 pm</t>
   </si>
   <si>
     <t>Jewellery Organizer</t>
@@ -82,10 +92,7 @@
     <t>organizer</t>
   </si>
   <si>
-    <t>6/27/2026, 5:25:32 PM</t>
-  </si>
-  <si>
-    <t>12/31/1969, 6:30:00 PM</t>
+    <t>18/7/2026, 4:44:23 pm</t>
   </si>
   <si>
     <t>SKU</t>
@@ -109,6 +116,43 @@
     <t>Badge</t>
   </si>
   <si>
+    <t>9372707b-71e1-4b1f-afd6-2628189bd090</t>
+  </si>
+  <si>
+    <t>0016</t>
+  </si>
+  <si>
+    <t>Multicolor Bangles (Set of 36 pcs)</t>
+  </si>
+  <si>
+    <t># Multi Color Bangles (Set of 36 pcs)
+## 🛍️ Product Details
+- **Price:** 760 Rs
+- **Color:** Multicolor
+- **Material:** Glass and metal type
+- **Size:** 2/4
+## ✨ Description
+- Delicate ghungroo(bell) embellishments create a melodious tinkling sound with every graceful movement of your wrist.
+- Crafted with meticulous attention to each bangle.
+- Intricately embraced with ghungroo and stone details.
+- Exceptional craftmanship to create a bold and eye-catching look.
+## 💎 Why Choose This?
+- Premium bangles set offered in a cost-effective range.
+- Perfect for festive occasions or weddings.</t>
+  </si>
+  <si>
+    <t>760</t>
+  </si>
+  <si>
+    <t>https://i.imgur.gg/noGuuZz-IMG_20260626_162815.jpg</t>
+  </si>
+  <si>
+    <t>premium</t>
+  </si>
+  <si>
+    <t>2/7/2026, 4:23:57 am</t>
+  </si>
+  <si>
     <t>b6589842-d5c9-4ca9-a52f-f3ba2b28e965</t>
   </si>
   <si>
@@ -118,7 +162,7 @@
     <t>Pearly Golden Clutch</t>
   </si>
   <si>
-    <t xml:space="preserve"># Pearly Golden Clutch
+    <t># Pearly Golden Clutch
 ## 🛍️ Product Details
 - **Price:** 1450Rs  
 - **Color:** Pearl &amp; Gold
@@ -145,13 +189,10 @@
     <t>https://i.imgur.gg/ISUicHP-IMG_20260705_164031.jpg</t>
   </si>
   <si>
-    <t>premium</t>
-  </si>
-  <si>
-    <t>7/15/2026, 5:11:44 AM</t>
-  </si>
-  <si>
-    <t>7/15/2026, 5:19:44 AM</t>
+    <t>15/7/2026, 5:11:44 am</t>
+  </si>
+  <si>
+    <t>15/7/2026, 5:19:44 am</t>
   </si>
   <si>
     <t>57fb626e-176f-4b78-8aff-069a614ab3ce</t>
@@ -163,7 +204,7 @@
     <t>Gold Sparkle Clutch</t>
   </si>
   <si>
-    <t xml:space="preserve"># Gold Sparkle Clutch
+    <t># Gold Sparkle Clutch
 ## 🛍️ Product Details
 - **Price:** 1050 Rs  
 - **Color:** Gold
@@ -189,10 +230,10 @@
     <t>https://i.imgur.gg/m7e3KzM-IMG_20260705_180129.jpg</t>
   </si>
   <si>
-    <t>7/17/2026, 5:16:05 AM</t>
-  </si>
-  <si>
-    <t>7/17/2026, 5:17:56 AM</t>
+    <t>17/7/2026, 5:16:05 am</t>
+  </si>
+  <si>
+    <t>17/7/2026, 5:17:56 am</t>
   </si>
   <si>
     <t>b08a25c6-fb0c-4d66-b027-0165834a13df</t>
@@ -204,7 +245,7 @@
     <t>Regal Pearl Clutch</t>
   </si>
   <si>
-    <t xml:space="preserve"># Regal Pearl Clutch
+    <t># Regal Pearl Clutch
 ## 🛍️ Product Details
 - **Price:** 2050 Rs  
 - **Color:** Silver
@@ -234,10 +275,10 @@
     <t>luxury</t>
   </si>
   <si>
-    <t>7/16/2026, 4:36:05 AM</t>
-  </si>
-  <si>
-    <t>7/16/2026, 5:52:30 AM</t>
+    <t>16/7/2026, 4:36:05 am</t>
+  </si>
+  <si>
+    <t>16/7/2026, 5:52:30 am</t>
   </si>
   <si>
     <t>7bd5f3da-d984-4a5f-98c7-e6e3c091f828</t>
@@ -249,7 +290,7 @@
     <t>Designer Bangle Organizer Box</t>
   </si>
   <si>
-    <t xml:space="preserve"># 6 – Rod Bangle Organizer
+    <t># 6 – Rod Bangle Organizer
 ## 📏 Dimensions
 - **Length:** 17 in / 44 cm
 - **Width:** 10 in / 26 cm
@@ -281,10 +322,10 @@
     <t>limited</t>
   </si>
   <si>
-    <t>6/27/2026, 5:31:28 PM</t>
-  </si>
-  <si>
-    <t>7/3/2026, 4:37:45 PM</t>
+    <t>27/6/2026, 5:31:28 pm</t>
+  </si>
+  <si>
+    <t>3/7/2026, 4:37:45 pm</t>
   </si>
   <si>
     <t>c6fd6319-543b-4e0e-85ff-8594885a526a</t>
@@ -296,7 +337,7 @@
     <t>Sparkly Rose Gold Clutch</t>
   </si>
   <si>
-    <t xml:space="preserve"># Sparkly Rose Gold Clutch
+    <t># Sparkly Rose Gold Clutch
 ## 🛍️ Product Details
 - **Price:** 850Rs  
 - **Color:** Rose Gold
@@ -321,10 +362,10 @@
     <t>https://i.imgur.gg/nlrXFTJ-IMG_20260705_174428.jpg</t>
   </si>
   <si>
-    <t>7/18/2026, 7:31:08 AM</t>
-  </si>
-  <si>
-    <t>7/18/2026, 8:26:00 AM</t>
+    <t>18/7/2026, 7:31:08 am</t>
+  </si>
+  <si>
+    <t>18/7/2026, 8:26:00 am</t>
   </si>
   <si>
     <t>f66837d7-4c09-4d84-8efe-a5cde13396be</t>
@@ -336,7 +377,7 @@
     <t>Silver Sparkle Clutch</t>
   </si>
   <si>
-    <t xml:space="preserve"># Silver Sparkle Clutch
+    <t># Silver Sparkle Clutch
 ## 🛍️ Product Details
 - **Price:** 1050 Rs  
 - **Color:** Silver
@@ -359,10 +400,10 @@
     <t>https://i.imgur.gg/Edoe0pu-IMG_20260705_175047.jpg</t>
   </si>
   <si>
-    <t>7/16/2026, 4:45:36 AM</t>
-  </si>
-  <si>
-    <t>7/17/2026, 5:02:05 AM</t>
+    <t>16/7/2026, 4:45:36 am</t>
+  </si>
+  <si>
+    <t>17/7/2026, 5:02:05 am</t>
   </si>
   <si>
     <t>ee181f87-c20a-42b9-ba7a-a3c49dd99c58</t>
@@ -374,7 +415,7 @@
     <t>Multicolor Bangles (set of 36 pcs)</t>
   </si>
   <si>
-    <t xml:space="preserve"># Multicolor Bangles (Set of 36pcs)
+    <t># Multicolor Bangles (Set of 36pcs)
 ## 🛍️ Product Details
 - **Price:** 860 Rs  
 - **Color:** Multicolor
@@ -396,47 +437,10 @@
     <t>https://i.imgur.gg/GUQy7if-WhatsApp_Image_2026-07-02_at_10.08.35_AM_(1).jpeg</t>
   </si>
   <si>
-    <t>7/2/2026, 4:58:20 AM</t>
-  </si>
-  <si>
-    <t>7/4/2026, 6:27:59 AM</t>
-  </si>
-  <si>
-    <t>9372707b-71e1-4b1f-afd6-2628189bd090</t>
-  </si>
-  <si>
-    <t>0016</t>
-  </si>
-  <si>
-    <t>Multicolor Bangles(Set of 32 pcs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Multi Color Bangles (Set of 32 pcs)
-## 🛍️ Product Details
-- **Price:** 760 Rs  
-- **Color:** Multicolor
-- **Material:** Glass and metal type  
-- **Size:** 2/4  
-## ✨ Description
-- Delicate ghungroo(bell) embellishments create a melodious tinkling sound with every graceful movement of your wrist.
-- Crafted with meticulous attention to each bangle.
-- Intricately embraced with ghungroo and stone details.
-- Exceptional craftsmanship to create a bold and eye-catching look.
-## 💎 Why Choose This?
-- Premium bangles set offered in a cost-effective range.
-- Perfect for festive occasions or weddings.</t>
-  </si>
-  <si>
-    <t>760</t>
-  </si>
-  <si>
-    <t>https://i.imgur.gg/noGuuZz-IMG_20260626_162815.jpg</t>
-  </si>
-  <si>
-    <t>7/2/2026, 4:23:57 AM</t>
-  </si>
-  <si>
-    <t>7/2/2026, 5:47:51 AM</t>
+    <t>2/7/2026, 4:58:20 am</t>
+  </si>
+  <si>
+    <t>4/7/2026, 6:27:59 am</t>
   </si>
   <si>
     <t>b6191e5f-945a-4cbd-87cb-c61dbf619f99</t>
@@ -448,7 +452,7 @@
     <t>Sparkly Gold Clutch</t>
   </si>
   <si>
-    <t xml:space="preserve"># Sparkly Gold Clutch
+    <t># Sparkly Gold Clutch
 ## 🛍️ Product Details
 - **Price:** 850Rs  
 - **Color:** Gold
@@ -470,10 +474,10 @@
     <t>https://i.imgur.gg/yqos8ez-IMG_20260705_175739.jpg</t>
   </si>
   <si>
-    <t>7/18/2026, 7:20:43 AM</t>
-  </si>
-  <si>
-    <t>7/18/2026, 8:23:10 AM</t>
+    <t>18/7/2026, 7:20:43 am</t>
+  </si>
+  <si>
+    <t>18/7/2026, 8:23:10 am</t>
   </si>
   <si>
     <t>1d8788a8-8fd1-4a48-a36a-51cd3784c97d</t>
@@ -482,7 +486,7 @@
     <t>0012</t>
   </si>
   <si>
-    <t xml:space="preserve"># 6 – Rod Bangle Organizer
+    <t># 6 – Rod Bangle Organizer
 ## 📏 Dimensions
 - **Length:** 17 in / 44 cm
 - **Width:** 10 in / 26 cm
@@ -508,57 +512,27 @@
     <t>https://i.imgur.gg/J2iAGgM-red-jewelry-box-front-view.jpg</t>
   </si>
   <si>
-    <t>6/27/2026, 6:07:37 PM</t>
-  </si>
-  <si>
-    <t>7/3/2026, 4:37:25 PM</t>
-  </si>
-  <si>
-    <t>4fff3e46-38ac-4d69-b6f1-bc731bcb2ad7</t>
-  </si>
-  <si>
-    <t>0015</t>
-  </si>
-  <si>
-    <t>Royal Queen Bangles (Set of 36 pcs)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Royal Queen Bangles (Set of 36pcs)
+    <t>27/6/2026, 6:07:37 pm</t>
+  </si>
+  <si>
+    <t>3/7/2026, 4:37:25 pm</t>
+  </si>
+  <si>
+    <t>150dc544-9a07-468c-8d71-8437ba6e1557</t>
+  </si>
+  <si>
+    <t>0017</t>
+  </si>
+  <si>
+    <t>Pink Velvet Bangle Set</t>
+  </si>
+  <si>
+    <t># Pink Velvet Bangles (Set of 18 pcs)
 ## 🛍️ Product Details
-- **Price:** 860 Rs  
-- **Color:** Bottle Green
-- **Material:**Glass &amp; metal type  
-- **Size:** 2/4  
-## ✨ Description
-- Crafted with meticulous attention to each bangle.
-- Intricately embellished with emerald, ruby, pearl and stone details.
-## 💎 Why Choose This?
-- Royal bangles set in a cost-effective range.
-- Exceptional craftmanship to create a bold and eye-catching look.
-- Unique premium collection and rare to find in other social platforms.</t>
-  </si>
-  <si>
-    <t>https://i.imgur.gg/4Io8TUt-WhatsApp_Image_2026-07-02_at_10.06.00_AM_(1).jpeg</t>
-  </si>
-  <si>
-    <t>7/2/2026, 4:50:52 AM</t>
-  </si>
-  <si>
-    <t>150dc544-9a07-468c-8d71-8437ba6e1557</t>
-  </si>
-  <si>
-    <t>0017</t>
-  </si>
-  <si>
-    <t>Pink Velvet Bangle Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Pink Velvet Bangles (Set of 18 pcs)
-## 🛍️ Product Details
-- **Price:** 860 Rs  
-- **Color:** Pink  
-- **Material:** Premium Velvet with metal type  
-- **Size:** 2/4  
+- **Price:** 860 Rs
+- **Color:** Pink
+- **Material:** Premium Velvet with metal type
+- **Size:** 2/4
 ## ✨ Description
 - Crafted with meticulous attention to each bangle.
 - Intricately embraced with kundan, pearl and stone details.
@@ -572,10 +546,10 @@
     <t>https://i.imgur.gg/cArGP3I-IMG_20260626_155904.jpg</t>
   </si>
   <si>
-    <t>7/1/2026, 5:23:39 PM</t>
-  </si>
-  <si>
-    <t>7/2/2026, 5:04:34 AM</t>
+    <t>1/7/2026, 5:23:39 pm</t>
+  </si>
+  <si>
+    <t>18/7/2026, 4:42:01 pm</t>
   </si>
   <si>
     <t>0e5be9d1-3d2f-4677-a59d-56d4af5d85a9</t>
@@ -587,7 +561,7 @@
     <t>Silver Fringe Clutch</t>
   </si>
   <si>
-    <t xml:space="preserve"># Silver Fringe Clutch
+    <t># Silver Fringe Clutch
 ## 🛍️ Product Details
 - **Price:** 1650Rs  
 - **Color:** Silver
@@ -611,10 +585,10 @@
     <t>https://i.imgur.gg/dEvA4vE-IMG_20260705_165128.jpg</t>
   </si>
   <si>
-    <t>7/5/2026, 3:49:40 PM</t>
-  </si>
-  <si>
-    <t>7/11/2026, 4:28:49 AM</t>
+    <t>5/7/2026, 3:49:40 pm</t>
+  </si>
+  <si>
+    <t>11/7/2026, 4:28:49 am</t>
   </si>
   <si>
     <t>3f414f79-b325-4330-b49c-e4e986ed3d0e</t>
@@ -626,7 +600,7 @@
     <t>Golden Luxe Pearl Clutch</t>
   </si>
   <si>
-    <t xml:space="preserve"># Golden Luxe Pearl Clutch
+    <t># Golden Luxe Pearl Clutch
 ## 🛍️ Product Details
 - **Price:** 1650 Rs  
 - **Color:** Gold
@@ -649,10 +623,10 @@
     <t>https://i.imgur.gg/YGmcHhj-IMG_20260705_163627.jpg</t>
   </si>
   <si>
-    <t>7/5/2026, 3:32:47 PM</t>
-  </si>
-  <si>
-    <t>7/7/2026, 5:04:56 AM</t>
+    <t>5/7/2026, 3:32:47 pm</t>
+  </si>
+  <si>
+    <t>7/7/2026, 5:04:56 am</t>
   </si>
   <si>
     <t>3860a6d8-3df7-4363-ae28-c6e7e346a3be</t>
@@ -664,7 +638,7 @@
     <t>Luxury Multicolor Sparkle Clutch</t>
   </si>
   <si>
-    <t xml:space="preserve"># Luxury Multicolor Sparkle Clutch
+    <t># Luxury Multicolor Sparkle Clutch
 ## 🛍️ Product Details
 - **Price:** 2050 Rs  
 - **Color:** Multicolor
@@ -689,10 +663,43 @@
     <t>https://i.imgur.gg/SAQefIg-IMG_20260705_173943.jpg</t>
   </si>
   <si>
-    <t>7/5/2026, 3:27:46 PM</t>
-  </si>
-  <si>
-    <t>7/7/2026, 5:06:15 AM</t>
+    <t>5/7/2026, 3:27:46 pm</t>
+  </si>
+  <si>
+    <t>7/7/2026, 5:06:15 am</t>
+  </si>
+  <si>
+    <t>4fff3e46-38ac-4d69-b6f1-bc731bcb2ad7</t>
+  </si>
+  <si>
+    <t>0015</t>
+  </si>
+  <si>
+    <t>Royal Queen Bangles (Set of 36 pcs)</t>
+  </si>
+  <si>
+    <t># Royal Queen Bangles (Set of 36pcs)
+## 🛍️ Product Details
+- **Price:** 860 Rs  
+- **Color:** Bottle Green
+- **Material:**Glass &amp; metal type  
+- **Size:** 2/4  
+## ✨ Description
+- Crafted with meticulous attention to each bangle.
+- Intricately embellished with emerald, ruby, pearl and stone details.
+## 💎 Why Choose This?
+- Royal bangles set in a cost-effective range.
+- Exceptional craftmanship to create a bold and eye-catching look.
+- Unique premium collection and rare to find in other social platforms.</t>
+  </si>
+  <si>
+    <t>https://i.imgur.gg/4Io8TUt-WhatsApp_Image_2026-07-02_at_10.06.00_AM_(1).jpeg</t>
+  </si>
+  <si>
+    <t>2/7/2026, 4:50:52 am</t>
+  </si>
+  <si>
+    <t>18/7/2026, 4:06:09 pm</t>
   </si>
   <si>
     <t>0048748f-a1ad-421f-b149-e5beb769b7c1</t>
@@ -704,7 +711,7 @@
     <t>Golden Eagle Glam Clutch</t>
   </si>
   <si>
-    <t xml:space="preserve"># Golden Eagle Glam Clutch
+    <t># Golden Eagle Glam Clutch
 ## 🛍️ Product Details
 - **Price:** 2050 Rs  
 - **Color:** Gold
@@ -728,10 +735,90 @@
     <t>https://i.imgur.gg/98usj1m-IMG_20260703_111740.jpg</t>
   </si>
   <si>
-    <t>7/5/2026, 3:39:03 PM</t>
-  </si>
-  <si>
-    <t>7/8/2026, 4:49:18 AM</t>
+    <t>5/7/2026, 3:39:03 pm</t>
+  </si>
+  <si>
+    <t>8/7/2026, 4:49:18 am</t>
+  </si>
+  <si>
+    <t>9f9d882a-b61f-476f-ad1e-6f6e5748b46f</t>
+  </si>
+  <si>
+    <t>0005</t>
+  </si>
+  <si>
+    <t>Golden Flower Glam Clutch</t>
+  </si>
+  <si>
+    <t># Golden Flower Glam Clutch
+## 🛍️ Product Details
+- **Price:** 2050 Rs  
+- **Color:** Gold
+## ✨ Features
+- Decorative lock, detachable gold chain, premium quality gold frame, metallic gold finish handle, designer gold fabric at the back.
+## ✨ Description
+- A Luxurious clutch in a glam look crafted with meticulous premium stone embellishment details.
+- A Structured rectangular shape &amp; a gold toned frame that makes it stand out as a statement.
+- Suits for luxury occasions, wedding, festive &amp; bridesmaid.
+- Premium shining stonework for a rich look.
+- Spacious yet compact size, easy to carry for events and functions.
+## 💎 Why Choose This Treasure?
+- Luxury clutch offered in a cost-effective range.
+- Crafted with meticulous attention.
+- Intricately embellished with premium stone details.
+- Exceptional craftsmanship to create a bold and eye-catching look.
+- Rare to find in other social platforms.
+- Premium gold finish and spacious to keep your things safe.</t>
+  </si>
+  <si>
+    <t>https://i.imgur.gg/KubkjRp-IMG_20260705_164746.jpg</t>
+  </si>
+  <si>
+    <t>12/7/2026, 4:04:54 pm</t>
+  </si>
+  <si>
+    <t>13/7/2026, 4:48:31 am</t>
+  </si>
+  <si>
+    <t>1f0ec4f5-fc3e-4d7e-9773-e3f92b4c2b86</t>
+  </si>
+  <si>
+    <t>0020</t>
+  </si>
+  <si>
+    <t>Regal Green Set</t>
+  </si>
+  <si>
+    <t># Regal Green Set
+## 🛍️ Product Details
+- **Price:** 449Rs  
+- **Color:** Premium Pearls with Green Stone
+## ✨ Features
+- Premium Pearl Necklace set, Luxurious touch with green stone detailing as center piece surrounded with stone details, Luxury packaging in velvet box for gifting.
+## ✨ Description
+- Elegant, handcrafted pearl necklace set with rich velvet box.
+- The Regal set features beautiful green stone detailing with premium traditional look.
+- This necklace set adds a royal touch to any ethnic outfit.
+- Lightweight classy and eye catchy.
+- Perfect for festive, gifting and any special occasion.
+## 💎 Why Choose This Treasure?
+- A graceful handcrafted regal green necklace set with a sparkling stone detail to enhance your look.
+- Crafted with meticulous attention.
+- Intricately embellished with premium pearls and green stone as center piece.
+- Exceptional craftsmanship to create a bold and eye-catching look.
+- Rare to find in other social platforms.</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>https://i.imgur.gg/XmbBFvK-IMG_20260705_191751.jpg</t>
+  </si>
+  <si>
+    <t>14/7/2026, 5:15:49 am</t>
+  </si>
+  <si>
+    <t>15/7/2026, 10:44:51 am</t>
   </si>
   <si>
     <t>44d71502-97b9-4e17-be41-42664b677959</t>
@@ -743,7 +830,7 @@
     <t>Floral Luxe Bracelet</t>
   </si>
   <si>
-    <t xml:space="preserve"># Floral Luxe Bracelet
+    <t># Floral Luxe Bracelet
 ## 🛍️ Product Details
 - **Price:** 299Rs
 - **Color:** Gold
@@ -770,73 +857,10 @@
     <t>https://i.imgur.gg/1XOqHkj-IMG_20260705_183745.jpg</t>
   </si>
   <si>
-    <t>7/12/2026, 6:16:30 AM</t>
-  </si>
-  <si>
-    <t>7/12/2026, 10:14:53 AM</t>
-  </si>
-  <si>
-    <t>b1bad34e-8295-494b-8f07-5eff7bbee63f</t>
-  </si>
-  <si>
-    <t>00112</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>7/12/2026, 5:08:15 PM</t>
-  </si>
-  <si>
-    <t>7/14/2026, 1:24:03 PM</t>
-  </si>
-  <si>
-    <t>9f9d882a-b61f-476f-ad1e-6f6e5748b46f</t>
-  </si>
-  <si>
-    <t>0005</t>
-  </si>
-  <si>
-    <t>Golden Flower Glam Clutch</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Golden Flower Glam Clutch
-## 🛍️ Product Details
-- **Price:** 2050 Rs  
-- **Color:** Gold
-## ✨ Features
-- Decorative lock, detachable gold chain, premium quality gold frame, metallic gold finish handle, designer gold fabric at the back.
-## ✨ Description
-- A Luxurious clutch in a glam look crafted with meticulous premium stone embellishment details.
-- A Structured rectangular shape &amp; a gold toned frame that makes it stand out as a statement.
-- Suits for luxury occasions, wedding, festive &amp; bridesmaid.
-- Premium shining stonework for a rich look.
-- Spacious yet compact size, easy to carry for events and functions.
-## 💎 Why Choose This Treasure?
-- Luxury clutch offered in a cost-effective range.
-- Crafted with meticulous attention.
-- Intricately embellished with premium stone details.
-- Exceptional craftsmanship to create a bold and eye-catching look.
-- Rare to find in other social platforms.
-- Premium gold finish and spacious to keep your things safe.</t>
-  </si>
-  <si>
-    <t>https://i.imgur.gg/KubkjRp-IMG_20260705_164746.jpg</t>
-  </si>
-  <si>
-    <t>7/12/2026, 4:04:54 PM</t>
-  </si>
-  <si>
-    <t>7/13/2026, 4:48:31 AM</t>
+    <t>12/7/2026, 6:16:30 am</t>
+  </si>
+  <si>
+    <t>18/7/2026, 4:08:25 pm</t>
   </si>
   <si>
     <t>afc4b808-ef31-497d-b2ea-03216e68487a</t>
@@ -848,7 +872,7 @@
     <t>Heart Luxe Bracelet</t>
   </si>
   <si>
-    <t xml:space="preserve"># Heart Luxe Bracelet
+    <t># Heart Luxe Bracelet
 ## 🛍️ Product Details
 - **Price:** 299 Rs  
 - **Color:** Gold
@@ -876,51 +900,10 @@
     <t>https://i.imgur.gg/vQKNhBB-IMG_20260705_182930.jpg</t>
   </si>
   <si>
-    <t>7/9/2026, 3:24:27 AM</t>
-  </si>
-  <si>
-    <t>7/13/2026, 9:04:09 AM</t>
-  </si>
-  <si>
-    <t>1f0ec4f5-fc3e-4d7e-9773-e3f92b4c2b86</t>
-  </si>
-  <si>
-    <t>0020</t>
-  </si>
-  <si>
-    <t>Regal Green Set</t>
-  </si>
-  <si>
-    <t xml:space="preserve"># Regal Green Set
-## 🛍️ Product Details
-- **Price:** 449Rs  
-- **Color:** Premium Pearls with Green Stone
-## ✨ Features
-- Premium Pearl Necklace set, Luxurious touch with green stone detailing as center piece surrounded with stone details, Luxury packaging in velvet box for gifting.
-## ✨ Description
-- Elegant, handcrafted pearl necklace set with rich velvet box.
-- The Regal set features beautiful green stone detailing with premium traditional look.
-- This necklace set adds a royal touch to any ethnic outfit.
-- Lightweight classy and eye catchy.
-- Perfect for festive, gifting and any special occasion.
-## 💎 Why Choose This Treasure?
-- A graceful handcrafted regal green necklace set with a sparkling stone detail to enhance your look.
-- Crafted with meticulous attention.
-- Intricately embellished with premium pearls and green stone as center piece.
-- Exceptional craftsmanship to create a bold and eye-catching look.
-- Rare to find in other social platforms.</t>
-  </si>
-  <si>
-    <t>449</t>
-  </si>
-  <si>
-    <t>https://i.imgur.gg/XmbBFvK-IMG_20260705_191751.jpg</t>
-  </si>
-  <si>
-    <t>7/14/2026, 5:15:49 AM</t>
-  </si>
-  <si>
-    <t>7/15/2026, 10:44:51 AM</t>
+    <t>9/7/2026, 3:24:27 am</t>
+  </si>
+  <si>
+    <t>18/7/2026, 4:08:57 pm</t>
   </si>
   <si>
     <t>Order Number</t>
@@ -1013,7 +996,7 @@
     <t>shipped</t>
   </si>
   <si>
-    <t>SRSP7452869877</t>
+    <t>2827792570832</t>
   </si>
   <si>
     <t>150</t>
@@ -1025,10 +1008,10 @@
     <t>pay_TDkY1cBs9hjhQa</t>
   </si>
   <si>
-    <t>7/15/2026, 10:44:50 AM</t>
-  </si>
-  <si>
-    <t>7/16/2026, 5:28:57 AM</t>
+    <t>15/7/2026, 10:44:50 am</t>
+  </si>
+  <si>
+    <t>18/7/2026, 4:45:58 pm</t>
   </si>
   <si>
     <t>506abb7a-5a8e-4965-bc80-c8d2000a96c5</t>
@@ -1037,48 +1020,9 @@
     <t>ORD-C966104D</t>
   </si>
   <si>
-    <t>Deepak</t>
-  </si>
-  <si>
-    <t>deepakinmail@gmail.com</t>
-  </si>
-  <si>
-    <t>9789801844</t>
-  </si>
-  <si>
-    <t>Tw</t>
-  </si>
-  <si>
-    <t>Hhh</t>
-  </si>
-  <si>
-    <t>Diglipur</t>
-  </si>
-  <si>
-    <t>AN</t>
-  </si>
-  <si>
-    <t>038282</t>
-  </si>
-  <si>
     <t>approved</t>
   </si>
   <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>210</t>
-  </si>
-  <si>
-    <t>pay_TCfYTF8IPI8Bhe</t>
-  </si>
-  <si>
-    <t>7/12/2026, 5:12:49 PM</t>
-  </si>
-  <si>
-    <t>7/12/2026, 5:16:27 PM</t>
-  </si>
-  <si>
     <t>Order ID</t>
   </si>
   <si>
@@ -1094,27 +1038,18 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>bf91efc0-35cc-443f-a496-2021e279c550</t>
-  </si>
-  <si>
     <t>525d1755-0626-4095-8604-5bbd14a8dc61</t>
   </si>
   <si>
     <t>Notes</t>
   </si>
   <si>
-    <t>98c8dc8a-18a1-4bec-9f3c-ca00f2ba7401</t>
-  </si>
-  <si>
     <t>pending</t>
   </si>
   <si>
     <t>Order placed</t>
   </si>
   <si>
-    <t>7b8b9bc3-3031-45d6-9438-c60d2e083454</t>
-  </si>
-  <si>
     <t>Status changed to approved</t>
   </si>
   <si>
@@ -1124,7 +1059,7 @@
     <t>be7f531e-ab81-46b3-832f-578a5d6150a3</t>
   </si>
   <si>
-    <t>7/15/2026, 11:12:03 AM</t>
+    <t>15/7/2026, 11:12:03 am</t>
   </si>
   <si>
     <t>4154d013-594d-4252-ba98-7c385a22ae0c</t>
@@ -1136,7 +1071,7 @@
     <t>Status changed to packaging</t>
   </si>
   <si>
-    <t>7/15/2026, 11:12:23 AM</t>
+    <t>15/7/2026, 11:12:23 am</t>
   </si>
   <si>
     <t>fa24f15a-2488-436a-9bc2-7d7605870023</t>
@@ -1145,6 +1080,9 @@
     <t>Status changed to shipped</t>
   </si>
   <si>
+    <t>16/7/2026, 5:28:57 am</t>
+  </si>
+  <si>
     <t>Username</t>
   </si>
   <si>
@@ -1169,10 +1107,10 @@
     <t>super_admin</t>
   </si>
   <si>
-    <t>7/18/2026, 4:55:39 AM</t>
-  </si>
-  <si>
-    <t>5/24/2026, 6:01:54 AM</t>
+    <t>18/7/2026, 4:28:12 pm</t>
+  </si>
+  <si>
+    <t>24/5/2026, 6:01:54 am</t>
   </si>
   <si>
     <t>Table</t>
@@ -1187,6 +1125,9 @@
     <t>Product</t>
   </si>
   <si>
+    <t>0016 - Multicolor Bangles (Set of 36 pcs)</t>
+  </si>
+  <si>
     <t>0006 - Pearly Golden Clutch</t>
   </si>
   <si>
@@ -1208,46 +1149,40 @@
     <t>0014 - Multicolor Bangles (set of 36 pcs)</t>
   </si>
   <si>
-    <t>0016 - Multicolor Bangles(Set of 32 pcs)</t>
-  </si>
-  <si>
     <t>0010 - Sparkly Gold Clutch</t>
   </si>
   <si>
     <t>0012 - Designer Bangle Organizer Box</t>
   </si>
   <si>
+    <t>0017 - Pink Velvet Bangle Set</t>
+  </si>
+  <si>
+    <t>0004 - Silver Fringe Clutch</t>
+  </si>
+  <si>
+    <t>0002 - Golden Luxe Pearl Clutch</t>
+  </si>
+  <si>
+    <t>0001 - Luxury Multicolor Sparkle Clutch</t>
+  </si>
+  <si>
     <t>0015 - Royal Queen Bangles (Set of 36 pcs)</t>
   </si>
   <si>
-    <t>0017 - Pink Velvet Bangle Set</t>
-  </si>
-  <si>
-    <t>0004 - Silver Fringe Clutch</t>
-  </si>
-  <si>
-    <t>0002 - Golden Luxe Pearl Clutch</t>
-  </si>
-  <si>
-    <t>0001 - Luxury Multicolor Sparkle Clutch</t>
-  </si>
-  <si>
     <t>0003 - Golden Eagle Glam Clutch</t>
   </si>
   <si>
+    <t>0005 - Golden Flower Glam Clutch</t>
+  </si>
+  <si>
+    <t>0020 - Regal Green Set</t>
+  </si>
+  <si>
     <t>0019 - Floral Luxe Bracelet</t>
   </si>
   <si>
-    <t>00112 - Test</t>
-  </si>
-  <si>
-    <t>0005 - Golden Flower Glam Clutch</t>
-  </si>
-  <si>
     <t>0018 - Heart Luxe Bracelet</t>
-  </si>
-  <si>
-    <t>0020 - Regal Green Set</t>
   </si>
   <si>
     <t>Admin</t>
@@ -1262,19 +1197,20 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1660,9 +1596,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -1673,7 +1609,7 @@
     <col min="7" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1699,7 +1635,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>4</v>
       </c>
@@ -1722,9 +1658,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -1739,21 +1675,21 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4">
         <v>3</v>
@@ -1762,21 +1698,21 @@
         <v>10</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -1788,43 +1724,20 @@
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -1840,36 +1753,36 @@
     <col min="12" max="13" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>5</v>
@@ -1881,15 +1794,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2">
         <v>4</v>
@@ -1898,31 +1811,31 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
       </c>
       <c r="L2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -1951,7 +1864,7 @@
         <v>44</v>
       </c>
       <c r="J3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K3" t="s">
         <v>10</v>
@@ -1963,7 +1876,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -1992,89 +1905,89 @@
         <v>52</v>
       </c>
       <c r="J4" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="K4" t="s">
         <v>10</v>
       </c>
       <c r="L4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M4" t="s">
         <v>54</v>
       </c>
-      <c r="M4" t="s">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>56</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>57</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
         <v>58</v>
       </c>
-      <c r="D5">
-        <v>25</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>59</v>
-      </c>
-      <c r="G5" t="s">
-        <v>60</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" t="s">
         <v>61</v>
-      </c>
-      <c r="J5" t="s">
-        <v>62</v>
       </c>
       <c r="K5" t="s">
         <v>10</v>
       </c>
       <c r="L5" t="s">
+        <v>62</v>
+      </c>
+      <c r="M5" t="s">
         <v>63</v>
       </c>
-      <c r="M5" t="s">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>65</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>66</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6">
+        <v>25</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
         <v>67</v>
       </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>68</v>
-      </c>
-      <c r="G6" t="s">
-        <v>69</v>
       </c>
       <c r="H6">
         <v>1</v>
       </c>
       <c r="I6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J6" t="s">
         <v>70</v>
-      </c>
-      <c r="J6" t="s">
-        <v>62</v>
       </c>
       <c r="K6" t="s">
         <v>10</v>
@@ -2086,7 +1999,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>73</v>
       </c>
@@ -2106,36 +2019,36 @@
         <v>76</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="H7">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J7" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="K7" t="s">
         <v>10</v>
       </c>
       <c r="L7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M7" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -2144,10 +2057,10 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G8" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2156,7 +2069,7 @@
         <v>85</v>
       </c>
       <c r="J8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K8" t="s">
         <v>10</v>
@@ -2168,7 +2081,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>88</v>
       </c>
@@ -2197,7 +2110,7 @@
         <v>93</v>
       </c>
       <c r="J9" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" t="s">
         <v>10</v>
@@ -2209,7 +2122,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>96</v>
       </c>
@@ -2229,7 +2142,7 @@
         <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -2238,7 +2151,7 @@
         <v>100</v>
       </c>
       <c r="J10" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K10" t="s">
         <v>10</v>
@@ -2250,7 +2163,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>103</v>
       </c>
@@ -2258,19 +2171,19 @@
         <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D11">
         <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
         <v>105</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -2279,7 +2192,7 @@
         <v>106</v>
       </c>
       <c r="J11" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K11" t="s">
         <v>10</v>
@@ -2291,7 +2204,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>109</v>
       </c>
@@ -2302,16 +2215,16 @@
         <v>111</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
         <v>112</v>
       </c>
       <c r="G12" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2320,7 +2233,7 @@
         <v>113</v>
       </c>
       <c r="J12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K12" t="s">
         <v>10</v>
@@ -2329,59 +2242,59 @@
         <v>114</v>
       </c>
       <c r="M12" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G13" t="s">
-        <v>84</v>
+        <v>120</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J13" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="K13" t="s">
         <v>10</v>
       </c>
       <c r="L13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M13" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -2390,39 +2303,39 @@
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G14" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J14" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K14" t="s">
         <v>10</v>
       </c>
       <c r="L14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M14" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -2431,80 +2344,80 @@
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G15" t="s">
-        <v>126</v>
+        <v>59</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J15" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K15" t="s">
         <v>10</v>
       </c>
       <c r="L15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M15" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="H16">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J16" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="K16" t="s">
         <v>10</v>
       </c>
       <c r="L16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M16" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D17">
         <v>4</v>
@@ -2513,39 +2426,39 @@
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="H17">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J17" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K17" t="s">
         <v>10</v>
       </c>
       <c r="L17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M17" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C18" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -2554,10 +2467,10 @@
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G18" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -2566,7 +2479,7 @@
         <v>156</v>
       </c>
       <c r="J18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K18" t="s">
         <v>10</v>
@@ -2578,7 +2491,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>159</v>
       </c>
@@ -2588,7 +2501,13 @@
       <c r="C19" t="s">
         <v>161</v>
       </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
       <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
         <v>162</v>
       </c>
       <c r="G19" t="s">
@@ -2597,8 +2516,14 @@
       <c r="H19">
         <v>0</v>
       </c>
+      <c r="I19" t="s">
+        <v>164</v>
+      </c>
+      <c r="J19" t="s">
+        <v>37</v>
+      </c>
       <c r="K19" t="s">
-        <v>164</v>
+        <v>10</v>
       </c>
       <c r="L19" t="s">
         <v>165</v>
@@ -2607,7 +2532,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>167</v>
       </c>
@@ -2618,129 +2543,88 @@
         <v>169</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F20" t="s">
         <v>170</v>
       </c>
       <c r="G20" t="s">
-        <v>51</v>
+        <v>171</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J20" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="K20" t="s">
         <v>10</v>
       </c>
       <c r="L20" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M20" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G21" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="H21">
         <v>0</v>
       </c>
       <c r="I21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J21" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K21" t="s">
         <v>10</v>
       </c>
       <c r="L21" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M21" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
         <v>181</v>
       </c>
-      <c r="B22" t="s">
-        <v>182</v>
-      </c>
-      <c r="C22" t="s">
-        <v>183</v>
-      </c>
-      <c r="D22">
-        <v>4</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>184</v>
-      </c>
-      <c r="G22" t="s">
-        <v>185</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22" t="s">
-        <v>186</v>
-      </c>
-      <c r="J22" t="s">
-        <v>36</v>
-      </c>
-      <c r="K22" t="s">
-        <v>10</v>
-      </c>
-      <c r="L22" t="s">
-        <v>187</v>
-      </c>
-      <c r="M22" t="s">
-        <v>188</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1"/>
+  <autoFilter ref="A1:M1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:U2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -2759,63 +2643,63 @@
     <col min="20" max="21" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>6</v>
@@ -2824,132 +2708,76 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H2" t="s">
         <v>207</v>
       </c>
-      <c r="B2" t="s">
+      <c r="I2" t="s">
         <v>208</v>
       </c>
-      <c r="C2" t="s">
+      <c r="J2" t="s">
         <v>209</v>
       </c>
-      <c r="D2" t="s">
+      <c r="K2" t="s">
         <v>210</v>
       </c>
-      <c r="E2" t="s">
+      <c r="L2" t="s">
         <v>211</v>
       </c>
-      <c r="F2" t="s">
+      <c r="M2" t="s">
         <v>212</v>
       </c>
-      <c r="G2" t="s">
+      <c r="N2" t="s">
+        <v>163</v>
+      </c>
+      <c r="O2" t="s">
         <v>213</v>
       </c>
-      <c r="H2" t="s">
+      <c r="P2" t="s">
         <v>214</v>
       </c>
-      <c r="I2" t="s">
+      <c r="Q2" t="s">
         <v>215</v>
       </c>
-      <c r="J2" t="s">
+      <c r="T2" t="s">
         <v>216</v>
       </c>
-      <c r="K2" t="s">
+      <c r="U2" t="s">
         <v>217</v>
       </c>
-      <c r="L2" t="s">
-        <v>218</v>
-      </c>
-      <c r="M2" t="s">
-        <v>219</v>
-      </c>
-      <c r="N2" t="s">
-        <v>185</v>
-      </c>
-      <c r="O2" t="s">
-        <v>220</v>
-      </c>
-      <c r="P2" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>222</v>
-      </c>
-      <c r="T2" t="s">
-        <v>223</v>
-      </c>
-      <c r="U2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>225</v>
-      </c>
-      <c r="B3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F3" t="s">
-        <v>230</v>
-      </c>
-      <c r="G3" t="s">
-        <v>231</v>
-      </c>
-      <c r="H3" t="s">
-        <v>232</v>
-      </c>
-      <c r="I3" t="s">
-        <v>233</v>
-      </c>
-      <c r="J3" t="s">
-        <v>234</v>
-      </c>
-      <c r="K3" t="s">
-        <v>217</v>
-      </c>
-      <c r="L3" t="s">
-        <v>235</v>
-      </c>
-      <c r="N3" t="s">
-        <v>163</v>
-      </c>
-      <c r="O3" t="s">
-        <v>236</v>
-      </c>
-      <c r="P3" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>238</v>
-      </c>
-      <c r="T3" t="s">
-        <v>239</v>
-      </c>
-      <c r="U3" t="s">
-        <v>240</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U1"/>
+  <autoFilter ref="A1:U1" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="40" customWidth="1"/>
@@ -2958,35 +2786,35 @@
     <col min="7" max="7" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="C2" t="s">
         <v>159</v>
@@ -3001,43 +2829,20 @@
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1"/>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -3045,136 +2850,102 @@
     <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="B2" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="C2" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="E2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C3" t="s">
-        <v>235</v>
-      </c>
-      <c r="D3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="E5" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" t="s">
-        <v>207</v>
-      </c>
-      <c r="C4" t="s">
-        <v>250</v>
-      </c>
-      <c r="D4" t="s">
-        <v>251</v>
-      </c>
-      <c r="E4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C5" t="s">
-        <v>235</v>
-      </c>
-      <c r="D5" t="s">
-        <v>253</v>
-      </c>
-      <c r="E5" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B6" t="s">
-        <v>207</v>
-      </c>
-      <c r="C6" t="s">
-        <v>258</v>
-      </c>
-      <c r="D6" t="s">
-        <v>259</v>
-      </c>
-      <c r="E6" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>261</v>
-      </c>
-      <c r="B7" t="s">
-        <v>207</v>
-      </c>
-      <c r="C7" t="s">
-        <v>218</v>
-      </c>
-      <c r="D7" t="s">
-        <v>262</v>
-      </c>
-      <c r="E7" t="s">
-        <v>224</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -3184,24 +2955,24 @@
     <col min="6" max="8" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -3210,63 +2981,63 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="D2" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="G2" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="H2" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C30"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="B2">
         <v>4</v>
@@ -3275,316 +3046,294 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B5">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>254</v>
+      </c>
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B10" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>254</v>
+      </c>
+      <c r="B11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>254</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>254</v>
+      </c>
+      <c r="B15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>254</v>
+      </c>
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C16" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>254</v>
+      </c>
+      <c r="B17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C17" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>254</v>
+      </c>
+      <c r="B18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C18" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>254</v>
+      </c>
+      <c r="B19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C19" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>254</v>
+      </c>
+      <c r="B20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B21" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>254</v>
+      </c>
+      <c r="B22" t="s">
+        <v>152</v>
+      </c>
+      <c r="C22" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>254</v>
+      </c>
+      <c r="B23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>254</v>
+      </c>
+      <c r="B24" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>254</v>
+      </c>
+      <c r="B25" t="s">
+        <v>175</v>
+      </c>
+      <c r="C25" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
         <v>275</v>
       </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>275</v>
-      </c>
-      <c r="B6">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C26" t="s">
         <v>276</v>
       </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>276</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B9" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>276</v>
-      </c>
-      <c r="B10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>276</v>
-      </c>
-      <c r="B11" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>276</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>276</v>
-      </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>276</v>
-      </c>
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>276</v>
-      </c>
-      <c r="B15" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>276</v>
-      </c>
-      <c r="B16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>276</v>
-      </c>
-      <c r="B17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>276</v>
-      </c>
-      <c r="B18" t="s">
-        <v>115</v>
-      </c>
-      <c r="C18" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>276</v>
-      </c>
-      <c r="B19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>276</v>
-      </c>
-      <c r="B20" t="s">
-        <v>130</v>
-      </c>
-      <c r="C20" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>276</v>
-      </c>
-      <c r="B21" t="s">
-        <v>137</v>
-      </c>
-      <c r="C21" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>276</v>
-      </c>
-      <c r="B22" t="s">
-        <v>144</v>
-      </c>
-      <c r="C22" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>276</v>
-      </c>
-      <c r="B23" t="s">
-        <v>151</v>
-      </c>
-      <c r="C23" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>276</v>
-      </c>
-      <c r="B24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C24" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>276</v>
-      </c>
-      <c r="B25" t="s">
-        <v>167</v>
-      </c>
-      <c r="C25" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>276</v>
-      </c>
-      <c r="B26" t="s">
-        <v>174</v>
-      </c>
-      <c r="C26" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>276</v>
-      </c>
       <c r="B27" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="C27" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="C28" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>300</v>
-      </c>
-      <c r="B29" t="s">
-        <v>207</v>
-      </c>
-      <c r="C29" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>300</v>
-      </c>
-      <c r="B30" t="s">
-        <v>225</v>
-      </c>
-      <c r="C30" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>